--- a/ReporteFlujoNaranja.xlsx
+++ b/ReporteFlujoNaranja.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t xml:space="preserve">ID GESTION</t>
   </si>
@@ -28,10 +28,10 @@
     <t xml:space="preserve">NO GESTION</t>
   </si>
   <si>
-    <t xml:space="preserve">NOMBRE BIACORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBDE de CLIENTE</t>
+    <t xml:space="preserve">NOMBRE BITACORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOMBRE de CLIENTE</t>
   </si>
   <si>
     <t xml:space="preserve">DUI</t>
@@ -43,30 +43,71 @@
     <t xml:space="preserve">TELEFONO</t>
   </si>
   <si>
-    <t xml:space="preserve">Formulario Apple Pay</t>
+    <t xml:space="preserve">¿Pregunta 1?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Pregunta 2?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Pregunta 3?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobado o Denegado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CreateBY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATECREATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulario Apple pay</t>
   </si>
   <si>
     <t xml:space="preserve">Prueba 1</t>
   </si>
   <si>
+    <t xml:space="preserve">SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACTEL791</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prueba 2</t>
   </si>
   <si>
+    <t xml:space="preserve">Si</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denegado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prueba 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/08/2024  17:50:00 a. m.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy\ hh:mm"/>
   </numFmts>
   <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -126,9 +167,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -148,106 +201,187 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="21.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="27.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="18.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="2" t="n">
         <v>1434325</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>43242</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>50284060</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>4073190320395090</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="2" t="n">
         <v>77777777</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>45517.0534722222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>4324342</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>43243</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="0" t="n">
+      <c r="B3" s="2" t="n">
+        <v>43242</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>50284060</v>
       </c>
-      <c r="F3" s="0" t="n">
-        <v>4073190320395090</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>77777778</v>
+      <c r="F3" s="1" t="n">
+        <v>4390750003526090</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>77777777</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>45517.0534722222</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
         <v>6786632</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>43244</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="0" t="n">
+      <c r="B4" s="2" t="n">
+        <v>43242</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>50284060</v>
       </c>
-      <c r="F4" s="0" t="n">
-        <v>4073190320395090</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>77777779</v>
+      <c r="F4" s="1" t="n">
+        <v>4390750005148810</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>77777777</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
